--- a/docs/downloads/04/tbl_class_marovoay_ampijoroa.xlsx
+++ b/docs/downloads/04/tbl_class_marovoay_ampijoroa.xlsx
@@ -394,14 +394,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="E2">
-        <v>1.6</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="3">
@@ -417,14 +417,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D3">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>90.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4">
@@ -440,14 +440,8 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>7.9</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -509,14 +503,8 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>2.9</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -578,14 +566,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E10">
-        <v>9.5</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="11">
@@ -596,19 +584,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11">
-        <v>4.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -624,7 +612,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D12">
@@ -642,7 +630,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -651,10 +639,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="E13">
-        <v>50</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -670,7 +658,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D14">
@@ -683,24 +671,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>70</v>
-      </c>
-      <c r="E15">
-        <v>90.90000000000001</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -716,14 +698,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>185</v>
       </c>
       <c r="E16">
-        <v>1.8</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -739,14 +721,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D17">
-        <v>185</v>
+        <v>30</v>
       </c>
       <c r="E17">
-        <v>84.09999999999999</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="18">
@@ -762,14 +744,8 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>30</v>
-      </c>
-      <c r="E18">
-        <v>13.6</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -780,19 +756,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="E19">
-        <v>0.5</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="20">
@@ -808,14 +784,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D20">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="E20">
-        <v>58.5</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="21">
@@ -831,14 +807,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D21">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="E21">
-        <v>36.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="22">
@@ -849,19 +825,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>145</v>
       </c>
       <c r="E22">
-        <v>4.9</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="23">
@@ -877,14 +853,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D23">
-        <v>145</v>
+        <v>96</v>
       </c>
       <c r="E23">
-        <v>51.1</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="24">
@@ -900,14 +876,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D24">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="E24">
-        <v>33.8</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="25">
@@ -918,19 +894,13 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>34</v>
-      </c>
-      <c r="E25">
-        <v>12</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -941,19 +911,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D26">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E26">
-        <v>3.2</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="27">
@@ -969,14 +939,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D27">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E27">
-        <v>55.6</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="28">
@@ -987,19 +957,13 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>12</v>
-      </c>
-      <c r="E28">
-        <v>44.4</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1015,14 +979,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D29">
-        <v>39</v>
+        <v>236</v>
       </c>
       <c r="E29">
-        <v>14.1</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="30">
@@ -1038,14 +1002,8 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>236</v>
-      </c>
-      <c r="E30">
-        <v>85.2</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1061,14 +1019,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E31">
-        <v>0.7</v>
+        <v>12.6</v>
       </c>
     </row>
   </sheetData>
